--- a/static/theory_question_bank/理论题批量导入模板.xlsx
+++ b/static/theory_question_bank/理论题批量导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="7320" windowHeight="6400"/>
   </bookViews>
   <sheets>
     <sheet name="导入模板" sheetId="2" r:id="rId1"/>
@@ -179,11 +179,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">填空处使用(1)、(2)、(3)…序号(使用英文括号)代表; </t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t xml:space="preserve">填空处使用(1)、(2)、(3)…序号(使用英文括号)代表; 若为简答题，小题处使用(1)、(2)、(3)…序号(使用英文括号)代表; </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>填写整数；</t>
     </r>
     <r>
@@ -203,6 +210,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>填写题目答案，若为
 选择题，则填写A-Z的字母；若为多选题有多个答案，则请用</t>
     </r>
@@ -807,17 +821,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -841,13 +848,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -999,14 +999,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1346,19 +1338,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1367,131 +1368,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1506,30 +1498,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -1551,9 +1540,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1881,7 +1867,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AI25"/>
-  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.3333333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="24.3333333333333" style="2" customWidth="1"/>
@@ -1932,7 +1918,7 @@
       <c r="AF1" s="3"/>
       <c r="AG1" s="3"/>
       <c r="AH1" s="3"/>
-      <c r="AI1" s="18"/>
+      <c r="AI1" s="16"/>
     </row>
     <row r="2" ht="127.25" customHeight="1" spans="1:35">
       <c r="A2" s="4" t="s">
@@ -1941,308 +1927,308 @@
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="17"/>
-      <c r="AI2" s="19"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="17"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="T3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="V3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="W3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="X3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Y3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="Z3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="9" t="s">
+      <c r="AA3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AB3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AC3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="AD3" s="9" t="s">
+      <c r="AD3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AE3" s="9" t="s">
+      <c r="AE3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AF3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AG3" s="9" t="s">
+      <c r="AG3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="9" t="s">
+      <c r="AH3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="AI3" s="9" t="s">
+      <c r="AI3" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="42.75" spans="1:35">
-      <c r="A4" s="12">
+    <row r="4" s="1" customFormat="1" ht="42" spans="1:35">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>2</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13" t="s">
+      <c r="H4" s="12"/>
+      <c r="I4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="13"/>
-      <c r="AG4" s="13"/>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="13"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="61.25" customHeight="1" spans="1:35">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>5</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13" t="s">
+      <c r="H5" s="12"/>
+      <c r="I5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12"/>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="12"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="36" customHeight="1" spans="1:11">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>2</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="12" t="s">
         <v>50</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -2253,28 +2239,28 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="61.25" customHeight="1" spans="1:9">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>74</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -2282,16 +2268,16 @@
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="38.5" customHeight="1" spans="1:9">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -2300,10 +2286,10 @@
       <c r="F8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="13" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -2311,7 +2297,7 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="114.5" customHeight="1" spans="1:9">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2320,19 +2306,19 @@
       <c r="C9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>83</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="13" t="s">
         <v>85</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -2340,52 +2326,52 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="7:7">
-      <c r="G10" s="15"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="7:7">
-      <c r="G11" s="15"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="7:7">
-      <c r="G12" s="15"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="7:7">
-      <c r="G13" s="15"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="7:7">
-      <c r="G14" s="15"/>
+      <c r="G14" s="14"/>
     </row>
     <row r="15" spans="7:7">
-      <c r="G15" s="16"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="7:7">
-      <c r="G16" s="16"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="7:7">
-      <c r="G17" s="16"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="7:7">
-      <c r="G18" s="16"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="7:7">
-      <c r="G19" s="16"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="7:7">
-      <c r="G20" s="16"/>
+      <c r="G20" s="15"/>
     </row>
     <row r="21" spans="7:7">
-      <c r="G21" s="16"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" spans="7:7">
-      <c r="G22" s="16"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="23" spans="7:7">
-      <c r="G23" s="16"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" spans="7:7">
-      <c r="G24" s="16"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="7:7">
-      <c r="G25" s="16"/>
+      <c r="G25" s="15"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
